--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,55 +787,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124125691</v>
+        <v>136768913</v>
       </c>
       <c r="B3" t="n">
-        <v>91930</v>
+        <v>83448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ödhult, Sm</t>
+          <t>Ingatorp, Ödhult, Bygdås, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525711</v>
+        <v>525675</v>
       </c>
       <c r="R3" t="n">
-        <v>6387268</v>
+        <v>6387176</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,12 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,72 +866,75 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av Linköpings stifts skogar</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124125691</t>
+          <t>https://artportalen.se/Sighting/136768913</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120454617</v>
+        <v>136768915</v>
       </c>
       <c r="B4" t="n">
-        <v>92567</v>
+        <v>83455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6031</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ingatorp, Sm</t>
+          <t>Ingatorp, Ödhult, Bygdås, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525724</v>
+        <v>525675</v>
       </c>
       <c r="R4" t="n">
-        <v>6387271</v>
+        <v>6387176</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,12 +958,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,65 +978,76 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johannes Glännman</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johannes Glännman, Helena Uhlén</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av Linköpings stifts skogar</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120454617</t>
+          <t>https://artportalen.se/Sighting/136768915</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120454618</v>
+        <v>124125691</v>
       </c>
       <c r="B5" t="n">
-        <v>99118</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ingatorp, Sm</t>
+          <t>Ödhult, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525708</v>
+        <v>525711</v>
       </c>
       <c r="R5" t="n">
-        <v>6387276</v>
+        <v>6387268</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,12 +1071,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,79 +1085,72 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johannes Glännman</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johannes Glännman, Helena Uhlén</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120454618</t>
+          <t>https://artportalen.se/Sighting/124125691</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124124884</v>
+        <v>136768912</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>92132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ödhult, Sm</t>
+          <t>Ingatorp, Ödhult, Bygdås, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525669</v>
+        <v>525675</v>
       </c>
       <c r="R6" t="n">
-        <v>6387029</v>
+        <v>6387176</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,77 +1188,72 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventering av Linköpings stifts skogar</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124124884</t>
+          <t>https://artportalen.se/Sighting/136768912</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124125017</v>
+        <v>120454617</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>92567</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ödhult, Sm</t>
+          <t>Ingatorp, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525659</v>
+        <v>525724</v>
       </c>
       <c r="R7" t="n">
-        <v>6387072</v>
+        <v>6387271</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,12 +1280,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,80 +1294,71 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Johannes Glännman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Johannes Glännman, Helena Uhlén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124125017</t>
+          <t>https://artportalen.se/Sighting/120454617</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124125235</v>
+        <v>136768911</v>
       </c>
       <c r="B8" t="n">
-        <v>99118</v>
+        <v>92789</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ödhult, Sm</t>
+          <t>Ingatorp, Ödhult, Bygdås, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525533</v>
+        <v>525675</v>
       </c>
       <c r="R8" t="n">
-        <v>6387109</v>
+        <v>6387176</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1396,12 +1382,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,73 +1403,69 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventering av Linköpings stifts skogar</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124125235</t>
+          <t>https://artportalen.se/Sighting/136768911</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124125315</v>
+        <v>136768914</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>83446</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ödhult, Sm</t>
+          <t>Ingatorp, Ödhult, Bygdås, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525471</v>
+        <v>525675</v>
       </c>
       <c r="R9" t="n">
-        <v>6387146</v>
+        <v>6387176</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,12 +1489,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,31 +1503,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventering av Linköpings stifts skogar</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124125315</t>
+          <t>https://artportalen.se/Sighting/136768914</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124125613</v>
+        <v>120454618</v>
       </c>
       <c r="B10" t="n">
         <v>99118</v>
@@ -1573,28 +1558,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ödhult, Sm</t>
+          <t>Ingatorp, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525629</v>
+        <v>525708</v>
       </c>
       <c r="R10" t="n">
-        <v>6387175</v>
+        <v>6387276</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1618,12 +1595,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,31 +1609,30 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Johannes Glännman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Johannes Glännman, Helena Uhlén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124125613</t>
+          <t>https://artportalen.se/Sighting/120454618</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124125688</v>
+        <v>124124884</v>
       </c>
       <c r="B11" t="n">
         <v>99118</v>
@@ -1686,7 +1662,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>108</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1699,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525711</v>
+        <v>525669</v>
       </c>
       <c r="R11" t="n">
-        <v>6387268</v>
+        <v>6387029</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1761,41 +1737,45 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124125688</t>
+          <t>https://artportalen.se/Sighting/124124884</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124125619</v>
+        <v>124125017</v>
       </c>
       <c r="B12" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1806,13 +1786,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525629</v>
+        <v>525659</v>
       </c>
       <c r="R12" t="n">
-        <v>6387175</v>
+        <v>6387072</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,13 +1848,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124125619</t>
+          <t>https://artportalen.se/Sighting/124125017</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124125728</v>
+        <v>124125235</v>
       </c>
       <c r="B13" t="n">
         <v>99118</v>
@@ -1904,7 +1884,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>137</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1917,13 +1897,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525812</v>
+        <v>525533</v>
       </c>
       <c r="R13" t="n">
-        <v>6387227</v>
+        <v>6387109</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1978,6 +1958,769 @@
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124125235</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124125315</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ödhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>525471</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6387146</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ingatorp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124125315</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124125613</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ödhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>525629</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6387175</v>
+      </c>
+      <c r="S15" t="n">
+        <v>100</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ingatorp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124125613</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124125688</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ödhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>525711</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6387268</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ingatorp</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124125688</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136768917</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ingatorp, Ödhult, Bygdås, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>525675</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6387176</v>
+      </c>
+      <c r="S17" t="n">
+        <v>100</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ingatorp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventering av Linköpings stifts skogar</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136768917</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124125619</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ödhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>525629</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6387175</v>
+      </c>
+      <c r="S18" t="n">
+        <v>100</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ingatorp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124125619</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136768916</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106492</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ingatorp, Ödhult, Bygdås, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>525675</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6387176</v>
+      </c>
+      <c r="S19" t="n">
+        <v>100</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ingatorp</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Inventering av Linköpings stifts skogar</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136768916</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124125728</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ödhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>525812</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6387227</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ingatorp</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/124125728</t>
         </is>
@@ -1997,6 +2740,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>136768912</v>
       </c>
       <c r="B6" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>136768911</v>
       </c>
       <c r="B8" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136768917</v>
       </c>
       <c r="B17" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>136768916</v>
       </c>
       <c r="B19" t="n">
-        <v>106492</v>
+        <v>106494</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136768913</v>
       </c>
       <c r="B3" t="n">
-        <v>83448</v>
+        <v>83452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136768915</v>
       </c>
       <c r="B4" t="n">
-        <v>83455</v>
+        <v>83459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136768912</v>
       </c>
       <c r="B6" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>136768911</v>
       </c>
       <c r="B8" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136768914</v>
       </c>
       <c r="B9" t="n">
-        <v>83446</v>
+        <v>83450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136768917</v>
       </c>
       <c r="B17" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>136768916</v>
       </c>
       <c r="B19" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136768913</v>
       </c>
       <c r="B3" t="n">
-        <v>83452</v>
+        <v>83454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136768915</v>
       </c>
       <c r="B4" t="n">
-        <v>83459</v>
+        <v>83461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136768912</v>
       </c>
       <c r="B6" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>136768911</v>
       </c>
       <c r="B8" t="n">
-        <v>92793</v>
+        <v>92795</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136768914</v>
       </c>
       <c r="B9" t="n">
-        <v>83450</v>
+        <v>83452</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136768917</v>
       </c>
       <c r="B17" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>136768916</v>
       </c>
       <c r="B19" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136768913</v>
       </c>
       <c r="B3" t="n">
-        <v>83454</v>
+        <v>83455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136768915</v>
       </c>
       <c r="B4" t="n">
-        <v>83461</v>
+        <v>83462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136768912</v>
       </c>
       <c r="B6" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>136768911</v>
       </c>
       <c r="B8" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136768914</v>
       </c>
       <c r="B9" t="n">
-        <v>83452</v>
+        <v>83453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136768917</v>
       </c>
       <c r="B17" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>136768916</v>
       </c>
       <c r="B19" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>136768912</v>
       </c>
       <c r="B6" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>136768911</v>
       </c>
       <c r="B8" t="n">
-        <v>92796</v>
+        <v>92802</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136768917</v>
       </c>
       <c r="B17" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>136768916</v>
       </c>
       <c r="B19" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136768913</v>
       </c>
       <c r="B3" t="n">
-        <v>83455</v>
+        <v>83459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136768915</v>
       </c>
       <c r="B4" t="n">
-        <v>83462</v>
+        <v>83466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136768912</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>136768911</v>
       </c>
       <c r="B8" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136768914</v>
       </c>
       <c r="B9" t="n">
-        <v>83453</v>
+        <v>83457</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136768917</v>
       </c>
       <c r="B17" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>136768916</v>
       </c>
       <c r="B19" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -2301,7 +2301,7 @@
         <v>136768917</v>
       </c>
       <c r="B17" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>136768916</v>
       </c>
       <c r="B19" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136768913</v>
       </c>
       <c r="B3" t="n">
-        <v>83459</v>
+        <v>83461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136768915</v>
       </c>
       <c r="B4" t="n">
-        <v>83466</v>
+        <v>83468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136768912</v>
       </c>
       <c r="B6" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>136768911</v>
       </c>
       <c r="B8" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136768914</v>
       </c>
       <c r="B9" t="n">
-        <v>83457</v>
+        <v>83459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136768917</v>
       </c>
       <c r="B17" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>136768916</v>
       </c>
       <c r="B19" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136768913</v>
       </c>
       <c r="B3" t="n">
-        <v>83461</v>
+        <v>83474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136768915</v>
       </c>
       <c r="B4" t="n">
-        <v>83468</v>
+        <v>83481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136768912</v>
       </c>
       <c r="B6" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>136768911</v>
       </c>
       <c r="B8" t="n">
-        <v>92808</v>
+        <v>92821</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136768914</v>
       </c>
       <c r="B9" t="n">
-        <v>83459</v>
+        <v>83472</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136768917</v>
       </c>
       <c r="B17" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>136768916</v>
       </c>
       <c r="B19" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136768913</v>
       </c>
       <c r="B3" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136768915</v>
       </c>
       <c r="B4" t="n">
-        <v>83481</v>
+        <v>83483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136768912</v>
       </c>
       <c r="B6" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>136768911</v>
       </c>
       <c r="B8" t="n">
-        <v>92821</v>
+        <v>92823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136768914</v>
       </c>
       <c r="B9" t="n">
-        <v>83472</v>
+        <v>83474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136768917</v>
       </c>
       <c r="B17" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>136768916</v>
       </c>
       <c r="B19" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136768913</v>
       </c>
       <c r="B3" t="n">
-        <v>83476</v>
+        <v>83479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136768915</v>
       </c>
       <c r="B4" t="n">
-        <v>83483</v>
+        <v>83486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136768912</v>
       </c>
       <c r="B6" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>136768911</v>
       </c>
       <c r="B8" t="n">
-        <v>92823</v>
+        <v>92826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136768914</v>
       </c>
       <c r="B9" t="n">
-        <v>83474</v>
+        <v>83477</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136768917</v>
       </c>
       <c r="B17" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>136768916</v>
       </c>
       <c r="B19" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136768913</v>
       </c>
       <c r="B3" t="n">
-        <v>83479</v>
+        <v>83489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136768915</v>
       </c>
       <c r="B4" t="n">
-        <v>83486</v>
+        <v>83496</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136768912</v>
       </c>
       <c r="B6" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>136768911</v>
       </c>
       <c r="B8" t="n">
-        <v>92826</v>
+        <v>92836</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136768914</v>
       </c>
       <c r="B9" t="n">
-        <v>83477</v>
+        <v>83487</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136768917</v>
       </c>
       <c r="B17" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>136768916</v>
       </c>
       <c r="B19" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>136768912</v>
       </c>
       <c r="B6" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>136768911</v>
       </c>
       <c r="B8" t="n">
-        <v>92836</v>
+        <v>92837</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136768917</v>
       </c>
       <c r="B17" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>136768916</v>
       </c>
       <c r="B19" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136768913</v>
       </c>
       <c r="B3" t="n">
-        <v>83489</v>
+        <v>83492</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136768915</v>
       </c>
       <c r="B4" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136768912</v>
       </c>
       <c r="B6" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>136768911</v>
       </c>
       <c r="B8" t="n">
-        <v>92837</v>
+        <v>92840</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136768914</v>
       </c>
       <c r="B9" t="n">
-        <v>83487</v>
+        <v>83490</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136768917</v>
       </c>
       <c r="B17" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>136768916</v>
       </c>
       <c r="B19" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30131-2023 artfynd.xlsx
+++ b/artfynd/A 30131-2023 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>136768912</v>
       </c>
       <c r="B6" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>136768911</v>
       </c>
       <c r="B8" t="n">
-        <v>92840</v>
+        <v>92842</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136768917</v>
       </c>
       <c r="B17" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>136768916</v>
       </c>
       <c r="B19" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
